--- a/data/trans_dic/P79$ninguna_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79$ninguna_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,92; 84,09</t>
+          <t>76,09; 82,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,84; 81,61</t>
+          <t>76,06; 80,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,82; 81,72</t>
+          <t>76,69; 80,74</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,17; 91,27</t>
+          <t>83,11; 86,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,72; 91,33</t>
+          <t>83,99; 86,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,77; 90,03</t>
+          <t>84,0; 86,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,31; 96,26</t>
+          <t>91,99; 95,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,92; 95,36</t>
+          <t>91,48; 95,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,83; 95,34</t>
+          <t>92,47; 95,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,13; 90,42</t>
+          <t>84,48; 87,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,7; 89,56</t>
+          <t>84,45; 86,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,24; 89,19</t>
+          <t>84,88; 86,6</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>398161</t>
+          <t>438317</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>568166</t>
+          <t>610624</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>966327</t>
+          <t>1048941</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>383479; 413826</t>
+          <t>419025; 455793</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>550236; 584391</t>
+          <t>593354; 629151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>940230; 987369</t>
+          <t>1020594; 1074548</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1943248</t>
+          <t>1829576</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1843926</t>
+          <t>1791743</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3787173</t>
+          <t>3621319</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1894884; 2030660</t>
+          <t>1792728; 1867547</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1802213; 1920284</t>
+          <t>1759355; 1822062</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3711641; 3895973</t>
+          <t>3571491; 3673494</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>606198</t>
+          <t>663291</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>604750</t>
+          <t>670339</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1210948</t>
+          <t>1333630</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>591467; 616764</t>
+          <t>648195; 676004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>592973; 615166</t>
+          <t>655645; 681738</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1193584; 1225910</t>
+          <t>1314310; 1350319</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2947606</t>
+          <t>2931184</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3016842</t>
+          <t>3072706</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5964448</t>
+          <t>6003890</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2892125; 3036240</t>
+          <t>2882657; 2979795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2968288; 3101973</t>
+          <t>3033076; 3113408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5882890; 6084284</t>
+          <t>5944978; 6065698</t>
         </is>
       </c>
     </row>
